--- a/Ноорог.xlsx
+++ b/Ноорог.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyamdavaa.e\Documents\Захирал\4\COr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8E98D85-2D77-4789-A37B-668FF1D801E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C8CE59-EABD-4C03-9A4F-EC4264EA5CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2DD40C02-F982-4E25-98DC-8DF0D23118A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{2DD40C02-F982-4E25-98DC-8DF0D23118A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
   <si>
     <t>Үлдсэн хугацааны ангилал</t>
   </si>
@@ -63,6 +64,24 @@
   </si>
   <si>
     <t xml:space="preserve">24 сараас дээш </t>
+  </si>
+  <si>
+    <t>Сар</t>
+  </si>
+  <si>
+    <t>Хугацаанаас өмнө</t>
+  </si>
+  <si>
+    <t>Алдагдал ҮЛД</t>
+  </si>
+  <si>
+    <t>Алдагдал</t>
+  </si>
+  <si>
+    <t>Дахин хөрөнгө оруулалт хийгээгүй үеийн алдагдал</t>
+  </si>
+  <si>
+    <t>DFC</t>
   </si>
 </sst>
 </file>
@@ -138,19 +157,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1613,4 +1635,619 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A901DA58-75AE-4F39-BA2F-A2C461754166}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="B2" s="1">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1">
+        <v>20.833333333333332</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1545257152.3020945</v>
+      </c>
+      <c r="E2" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>194913991.96421432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>15.433333333333334</v>
+      </c>
+      <c r="B3" s="1">
+        <v>60</v>
+      </c>
+      <c r="C3" s="1">
+        <v>44.566666666666663</v>
+      </c>
+      <c r="D3" s="1">
+        <v>86185689.530075833</v>
+      </c>
+      <c r="E3" s="4">
+        <v>7.7113799999999996E-2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>25162895.86795162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>23.7</v>
+      </c>
+      <c r="B4" s="1">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5457012.7432140112</v>
+      </c>
+      <c r="E4" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>20595.725617630356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>22.433333333333334</v>
+      </c>
+      <c r="B5" s="1">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.5666666666666664</v>
+      </c>
+      <c r="D5" s="1">
+        <v>30822003.240767896</v>
+      </c>
+      <c r="E5" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>348982.97929868364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>10.466666666666667</v>
+      </c>
+      <c r="B6" s="1">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1">
+        <v>25.533333333333331</v>
+      </c>
+      <c r="D6" s="1">
+        <v>152106186.7566146</v>
+      </c>
+      <c r="E6" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>23627738.75952683</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>7.7333333333333334</v>
+      </c>
+      <c r="B7" s="1">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23.266666666666666</v>
+      </c>
+      <c r="D7" s="1">
+        <v>22243467125.106037</v>
+      </c>
+      <c r="E7" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3141525661.4730573</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>10899794879.629629</v>
+      </c>
+      <c r="D10">
+        <v>2336039812.3510199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>39072180148.449471</v>
+      </c>
+      <c r="D11">
+        <v>15620941812.263161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>6156537863.4259262</v>
+      </c>
+      <c r="D12">
+        <v>3148556651.703774</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>4.0666666666666664</v>
+      </c>
+      <c r="B16" s="1">
+        <v>180</v>
+      </c>
+      <c r="C16" s="1">
+        <v>175.93333333333334</v>
+      </c>
+      <c r="D16" s="1">
+        <v>734616359.98933756</v>
+      </c>
+      <c r="E16" s="4">
+        <v>8.0234600000000003E-2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>876920767.53834975</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>23.866666666666667</v>
+      </c>
+      <c r="B17" s="1">
+        <v>24</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.13333333333333286</v>
+      </c>
+      <c r="D17" s="1">
+        <v>17507244.17168045</v>
+      </c>
+      <c r="E17" s="4">
+        <v>7.15253E-2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>48697.090227049281</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>23.7</v>
+      </c>
+      <c r="B18" s="1">
+        <v>24</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="D18" s="1">
+        <v>13899621.049774408</v>
+      </c>
+      <c r="E18" s="4">
+        <v>7.15253E-2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>52470.324288769894</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>12.866666666666667</v>
+      </c>
+      <c r="B19" s="1">
+        <v>24</v>
+      </c>
+      <c r="C19" s="1">
+        <v>11.133333333333333</v>
+      </c>
+      <c r="D19" s="1">
+        <v>417490653.70856071</v>
+      </c>
+      <c r="E19" s="4">
+        <v>7.8263299999999994E-2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>31222009.777127456</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="B20" s="1">
+        <v>24</v>
+      </c>
+      <c r="C20" s="1">
+        <v>17.666666666666668</v>
+      </c>
+      <c r="D20" s="1">
+        <v>745725843.37855387</v>
+      </c>
+      <c r="E20" s="4">
+        <v>8.0234600000000003E-2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>89749522.129711375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="B21" s="1">
+        <v>24</v>
+      </c>
+      <c r="C21" s="1">
+        <v>20.833333333333332</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1545257152.3020945</v>
+      </c>
+      <c r="E21" s="4">
+        <v>8.0234600000000003E-2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>218692394.00050554</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>15.433333333333334</v>
+      </c>
+      <c r="B22" s="1">
+        <v>60</v>
+      </c>
+      <c r="C22" s="1">
+        <v>44.566666666666663</v>
+      </c>
+      <c r="D22" s="1">
+        <v>86185689.530075833</v>
+      </c>
+      <c r="E22" s="4">
+        <v>7.7113799999999996E-2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>25162895.86795162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>23.666666666666668</v>
+      </c>
+      <c r="B23" s="1">
+        <v>24</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.33333333333333215</v>
+      </c>
+      <c r="D23" s="1">
+        <v>161146806.28460121</v>
+      </c>
+      <c r="E23" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F23" s="1">
+        <v>640206.71778756834</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="B24" s="1">
+        <v>24</v>
+      </c>
+      <c r="C24" s="1">
+        <v>22.6</v>
+      </c>
+      <c r="D24" s="1">
+        <v>944367104.06634343</v>
+      </c>
+      <c r="E24" s="4">
+        <v>8.0234600000000003E-2</v>
+      </c>
+      <c r="F24" s="1">
+        <v>144806641.08713877</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>23.833333333333332</v>
+      </c>
+      <c r="B25" s="1">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.16666666666666785</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1212552.6025823951</v>
+      </c>
+      <c r="E25" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3612.9368915620362</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>23.7</v>
+      </c>
+      <c r="B26" s="1">
+        <v>24</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="D26" s="1">
+        <v>5457012.7432140112</v>
+      </c>
+      <c r="E26" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>20595.725617630356</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>22.433333333333334</v>
+      </c>
+      <c r="B27" s="1">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1.5666666666666664</v>
+      </c>
+      <c r="D27" s="1">
+        <v>30822003.240767896</v>
+      </c>
+      <c r="E27" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>348982.97929868364</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>13.666666666666666</v>
+      </c>
+      <c r="B28" s="1">
+        <v>120</v>
+      </c>
+      <c r="C28" s="1">
+        <v>106.33333333333333</v>
+      </c>
+      <c r="D28" s="1">
+        <v>420564324.57752281</v>
+      </c>
+      <c r="E28" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F28" s="1">
+        <v>270840725.70590144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>10.466666666666667</v>
+      </c>
+      <c r="B29" s="1">
+        <v>36</v>
+      </c>
+      <c r="C29" s="1">
+        <v>25.533333333333331</v>
+      </c>
+      <c r="D29" s="1">
+        <v>152106186.7566146</v>
+      </c>
+      <c r="E29" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>23627738.75952683</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>7.7333333333333334</v>
+      </c>
+      <c r="B30" s="1">
+        <v>31</v>
+      </c>
+      <c r="C30" s="1">
+        <v>23.266666666666666</v>
+      </c>
+      <c r="D30" s="1">
+        <v>22243467125.106037</v>
+      </c>
+      <c r="E30" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>3141525661.4730573</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="B31" s="1">
+        <v>27</v>
+      </c>
+      <c r="C31" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="D31" s="1">
+        <v>12451691103.170471</v>
+      </c>
+      <c r="E31" s="4">
+        <v>7.1510699999999996E-2</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1637400264.708689</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>10899794879.629629</v>
+      </c>
+      <c r="D37">
+        <v>2336039812.3510199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38">
+        <v>39072180148.449471</v>
+      </c>
+      <c r="D38">
+        <v>15620941812.263161</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>6156537863.4259262</v>
+      </c>
+      <c r="D39">
+        <v>3148556651.703774</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Ноорог.xlsx
+++ b/Ноорог.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyamdavaa.e\Documents\Захирал\4\COr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blackmamba\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C8CE59-EABD-4C03-9A4F-EC4264EA5CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD9693A-5F2A-4F88-B943-FA7864891059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{2DD40C02-F982-4E25-98DC-8DF0D23118A6}"/>
+    <workbookView xWindow="4905" yWindow="1965" windowWidth="21660" windowHeight="11295" activeTab="1" xr2:uid="{2DD40C02-F982-4E25-98DC-8DF0D23118A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$15:$F$31</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,15 +38,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="13">
   <si>
     <t>Үлдсэн хугацааны ангилал</t>
   </si>
@@ -162,12 +162,13 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -217,7 +218,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Чөлөөлөгдсөн эх үүсвэр </c:v>
+                  <c:v>Чөлөөлөгдсөн эх үүсвэр</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -241,13 +242,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v> 12 сараас доош </c:v>
+                  <c:v>12 сараас доош</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 24 сараас доош </c:v>
+                  <c:v>24 сараас доош</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 24 сараас дээш  </c:v>
+                  <c:v>24 сараас дээш </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -256,7 +257,7 @@
             <c:numRef>
               <c:f>[1]GRAPH!$D$8:$D$10</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>10899794879.629629</c:v>
@@ -285,7 +286,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Дахин байршуулалт хийгдээгүй үеийн алдагдал </c:v>
+                  <c:v>Дахин байршуулалт хийгдээгүй үеийн алдагдал</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -306,13 +307,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v> 12 сараас доош </c:v>
+                  <c:v>12 сараас доош</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 24 сараас доош </c:v>
+                  <c:v>24 сараас доош</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 24 сараас дээш  </c:v>
+                  <c:v>24 сараас дээш </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -321,7 +322,7 @@
             <c:numRef>
               <c:f>[1]GRAPH!$E$8:$E$10</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>2336039812.3510199</c:v>
@@ -488,6 +489,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -495,6 +497,438 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Чөлөөлөгдсөн эх үүсвэр</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00,,," sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$40:$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>12 сараас доош</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24 сараас доош</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$40:$B$41</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>38817230874.769455</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1154285907.9087796</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CDE9-481F-8E4D-40D378A0F22A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Дахин байршуулалт хийгдээгүй үеийн алдагдал</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00,,," sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$40:$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>12 сараас доош</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24 сараас доош</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$40:$C$41</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>6132722989.6969776</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>328340197.12509179</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CDE9-481F-8E4D-40D378A0F22A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1476749840"/>
+        <c:axId val="1349446288"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1476749840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1349446288"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1349446288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="40000000000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="_(* #,##0.00,,,_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1476749840"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -563,7 +997,552 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1111,11 +2090,53 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1271866</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>169208</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1277470</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>54908</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8BE28B3-2F18-AE45-0DB4-6E075BF0B582}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Үлдэгдэл"/>
@@ -1505,15 +2526,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8BB706-A1DF-44EC-AA29-40DC21274582}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1527,11 +2548,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="5">
         <v>36</v>
       </c>
       <c r="C2" s="3">
@@ -1541,11 +2562,11 @@
         <v>2336039812.3510199</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="5">
         <v>146</v>
       </c>
       <c r="C3" s="3">
@@ -1555,11 +2576,11 @@
         <v>15620941812.263161</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="5">
         <v>11</v>
       </c>
       <c r="C4" s="3">
@@ -1569,7 +2590,7 @@
         <v>3148556651.703774</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +2601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1597,7 +2618,7 @@
         <v>2336039812.3510199</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1614,7 +2635,7 @@
         <v>15620941812.263161</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1639,18 +2660,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A901DA58-75AE-4F39-BA2F-A2C461754166}">
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1670,7 +2693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>3.1666666666666665</v>
       </c>
@@ -1690,7 +2713,7 @@
         <v>194913991.96421432</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>15.433333333333334</v>
       </c>
@@ -1710,7 +2733,7 @@
         <v>25162895.86795162</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>23.7</v>
       </c>
@@ -1730,7 +2753,7 @@
         <v>20595.725617630356</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>22.433333333333334</v>
       </c>
@@ -1750,7 +2773,7 @@
         <v>348982.97929868364</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>10.466666666666667</v>
       </c>
@@ -1770,7 +2793,7 @@
         <v>23627738.75952683</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>7.7333333333333334</v>
       </c>
@@ -1790,12 +2813,12 @@
         <v>3141525661.4730573</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -1809,7 +2832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1823,7 +2846,7 @@
         <v>2336039812.3510199</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1837,7 +2860,7 @@
         <v>15620941812.263161</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1851,7 +2874,7 @@
         <v>3148556651.703774</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1871,7 +2894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>4.0666666666666664</v>
       </c>
@@ -1891,7 +2914,7 @@
         <v>876920767.53834975</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>23.866666666666667</v>
       </c>
@@ -1911,7 +2934,7 @@
         <v>48697.090227049281</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>23.7</v>
       </c>
@@ -1931,7 +2954,7 @@
         <v>52470.324288769894</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>12.866666666666667</v>
       </c>
@@ -1951,7 +2974,7 @@
         <v>31222009.777127456</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>6.333333333333333</v>
       </c>
@@ -1971,7 +2994,7 @@
         <v>89749522.129711375</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3.1666666666666665</v>
       </c>
@@ -1991,7 +3014,7 @@
         <v>218692394.00050554</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>15.433333333333334</v>
       </c>
@@ -2011,7 +3034,7 @@
         <v>25162895.86795162</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>23.666666666666668</v>
       </c>
@@ -2031,7 +3054,7 @@
         <v>640206.71778756834</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>1.4</v>
       </c>
@@ -2051,7 +3074,7 @@
         <v>144806641.08713877</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23.833333333333332</v>
       </c>
@@ -2071,7 +3094,7 @@
         <v>3612.9368915620362</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>23.7</v>
       </c>
@@ -2091,7 +3114,7 @@
         <v>20595.725617630356</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>22.433333333333334</v>
       </c>
@@ -2111,7 +3134,7 @@
         <v>348982.97929868364</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>13.666666666666666</v>
       </c>
@@ -2131,7 +3154,7 @@
         <v>270840725.70590144</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>10.466666666666667</v>
       </c>
@@ -2151,7 +3174,7 @@
         <v>23627738.75952683</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>7.7333333333333334</v>
       </c>
@@ -2171,7 +3194,7 @@
         <v>3141525661.4730573</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5.3</v>
       </c>
@@ -2191,7 +3214,7 @@
         <v>1637400264.708689</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -2205,49 +3228,88 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
       <c r="B37">
         <v>7</v>
       </c>
-      <c r="C37">
-        <v>10899794879.629629</v>
-      </c>
-      <c r="D37">
-        <v>2336039812.3510199</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C37" s="1">
+        <v>38817230874.769455</v>
+      </c>
+      <c r="D37" s="1">
+        <v>6132722989.6969776</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
       <c r="B38">
+        <v>9</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1154285907.9087796</v>
+      </c>
+      <c r="D38" s="1">
+        <v>328340197.12509179</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
         <v>3</v>
       </c>
-      <c r="C38">
-        <v>39072180148.449471</v>
-      </c>
-      <c r="D38">
-        <v>15620941812.263161</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39">
+      <c r="F39" s="1">
+        <f>SUBTOTAL(9, D16:D31)</f>
         <v>0</v>
       </c>
-      <c r="C39">
-        <v>6156537863.4259262</v>
-      </c>
-      <c r="D39">
-        <v>3148556651.703774</v>
+      <c r="G39" s="1">
+        <f>SUBTOTAL(9, E16:E31)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <f>SUBTOTAL(9, F16:F31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="1">
+        <v>38817230874.769455</v>
+      </c>
+      <c r="C40" s="1">
+        <v>6132722989.6969776</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1154285907.9087796</v>
+      </c>
+      <c r="C41" s="1">
+        <v>328340197.12509179</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A15:F31" xr:uid="{A901DA58-75AE-4F39-BA2F-A2C461754166}">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="greaterThanOrEqual" val="24"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>